--- a/output/APTP_Completed_Form.xlsx
+++ b/output/APTP_Completed_Form.xlsx
@@ -3218,16 +3218,8 @@
           <t xml:space="preserve">  M  </t>
         </is>
       </c>
-      <c r="I18" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     F</t>
-        </is>
-      </c>
-      <c r="J18" s="174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      YES</t>
-        </is>
-      </c>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="174" t="inlineStr"/>
       <c r="K18" s="286" t="n"/>
       <c r="L18" s="308" t="inlineStr">
         <is>
@@ -3274,7 +3266,11 @@
       <c r="T19" s="76" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="75">
-      <c r="A20" s="285" t="n"/>
+      <c r="A20" s="285" t="inlineStr">
+        <is>
+          <t>New Jersey Manufacturers NJM - Auto Only E1118</t>
+        </is>
+      </c>
       <c r="B20" s="286" t="n"/>
       <c r="C20" s="286" t="n"/>
       <c r="D20" s="286" t="n"/>
